--- a/human_resources_forms/050_mid_year_performance_review_form--human_resources_forms.xlsx
+++ b/human_resources_forms/050_mid_year_performance_review_form--human_resources_forms.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>performance_review_form_page_1</t>
+          <t>employee_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>performance_review_form</t>
+          <t>Employee Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -533,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>performance_review_form_page_2</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>performance_review_form</t>
+          <t>Job Title</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -556,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>performance_review_form_page_3</t>
+          <t>performance_score</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>performance_review_form</t>
+          <t>Current Performance Score (1-5)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -579,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>performance_review_form_page_4</t>
+          <t>strengths</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>performance_review_form</t>
+          <t>Strengths</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -602,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>performance_review_form_page_5</t>
+          <t>development_areas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>performance_review_form</t>
+          <t>Development Areas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -625,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>performance_review_form_page_6</t>
+          <t>goals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>performance_review_form</t>
+          <t>Goals for the next 6 months</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -648,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>performance_review_form_page_7</t>
+          <t>professional_development</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>performance_review_form</t>
+          <t>Recommendations for Professional Development</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>performance_review_form_page_8</t>
+          <t>feedback_from_employee</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>performance_review_form</t>
+          <t>Feedback from the Employee</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -694,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>performance_review_form_page_9</t>
+          <t>feedback_from_manager</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>performance_review_form</t>
+          <t>Feedback from the Manager</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -717,18 +727,64 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>performance_review_form_page_10</t>
+          <t>action_items</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>performance_review_form</t>
+          <t>Action Items for the Manager</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>next_review_date</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Next Review Date</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>review_status</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Overall Performance Review Status</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -738,6 +794,93 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>review_status_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>review_status_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>review_status_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
